--- a/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/TERMINAL DE CAÑO PARA CORTINA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/TERMINAL DE CAÑO PARA CORTINA DISMAY.xlsx
@@ -775,14 +775,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45154.58670346592</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="10" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -804,8 +800,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="24">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -821,22 +815,6 @@
       </c>
       <c r="B12" s="6" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="24">
       <c r="A29" s="19" t="inlineStr">
         <is>
@@ -893,7 +871,6 @@
     <row r="32" ht="18" customHeight="1" s="24">
       <c r="E32" s="7" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="24">
       <c r="A34" s="8" t="inlineStr">
         <is>
@@ -908,9 +885,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -920,8 +894,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
